--- a/sheet/fitfactoros-template.xlsx
+++ b/sheet/fitfactoros-template.xlsx
@@ -268,7 +268,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Paste Intake's answer block into B3. Type your Gmail address in B2 during setup.</t>
+        <t>Paste Intake's answer block into B2. Your answers fill B2 through B19.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -716,12 +716,12 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Turn 1</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>Filled in during setup. Email links across the sheet use this so the right inbox opens.</t>
+          <t>Used only to build links that open your own inbox. Goes in your own Sheet.</t>
         </is>
       </c>
     </row>
@@ -1072,6 +1072,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="9">
       <c r="A21" s="15" t="inlineStr">
         <is>
@@ -1082,30 +1083,26 @@
     <row r="22" ht="15" customHeight="1" s="9">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>1. During setup, type your Gmail address in B2.</t>
+          <t>1. After Intake, click B2 and paste the answer block. Your answers fill B2 through B19.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="9">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2. After Intake, click B3 and paste the answer block. Each answer lands on its row.</t>
+          <t>2. To change one answer later, ask Claude to 'update my profile'. It tells you which cell to paste into.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="9">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>3. To change one answer later, ask Claude to 'update my profile'. It tells you which cell to paste into.</t>
+          <t>Yellow cells are yours to fill. Column C is a fictional example.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="9">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Yellow cells are yours to fill. Column C is a fictional example.</t>
-        </is>
-      </c>
+      <c r="A25" s="16" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/sheet/fitfactoros-template.xlsx
+++ b/sheet/fitfactoros-template.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26.85" customHeight="1" s="9">
+    <row r="2" s="9">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Gmail address (for inbox links)</t>
@@ -725,7 +725,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
+    <row r="3" s="9">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Your name</t>
@@ -744,7 +744,7 @@
       </c>
       <c r="E3" s="14" t="n"/>
     </row>
-    <row r="4" ht="26.85" customHeight="1" s="9">
+    <row r="4" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Resume file</t>
@@ -767,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="26.85" customHeight="1" s="9">
+    <row r="5" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Most recent role</t>
@@ -786,7 +786,7 @@
       </c>
       <c r="E5" s="14" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="9">
+    <row r="6" s="9">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Years of experience</t>
@@ -795,7 +795,7 @@
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>About 9 (estimate)</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E6" s="14" t="n"/>
     </row>
-    <row r="7" ht="26.85" customHeight="1" s="9">
+    <row r="7" s="9">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Top skills</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="E7" s="14" t="n"/>
     </row>
-    <row r="8" ht="26.85" customHeight="1" s="9">
+    <row r="8" s="9">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Target roles</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="E8" s="14" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="9">
+    <row r="9" s="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Where you can work</t>
@@ -862,7 +862,7 @@
       </c>
       <c r="E9" s="14" t="n"/>
     </row>
-    <row r="10" ht="26.85" customHeight="1" s="9">
+    <row r="10" s="9">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Pay floor</t>
@@ -885,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="9">
+    <row r="11" s="9">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Deal-breakers</t>
@@ -904,7 +904,7 @@
       </c>
       <c r="E11" s="14" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="9">
+    <row r="12" s="9">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Companies to avoid</t>
@@ -923,7 +923,7 @@
       </c>
       <c r="E12" s="14" t="n"/>
     </row>
-    <row r="13" ht="26.85" customHeight="1" s="9">
+    <row r="13" s="9">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Work that makes you lose track of time</t>
@@ -942,7 +942,7 @@
       </c>
       <c r="E13" s="14" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="9">
+    <row r="14" s="9">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Dream companies</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="E14" s="14" t="n"/>
     </row>
-    <row r="15" ht="26.85" customHeight="1" s="9">
+    <row r="15" s="9">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>People you know (and where)</t>
@@ -984,7 +984,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="9">
+    <row r="16" s="9">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>State</t>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E16" s="14" t="n"/>
     </row>
-    <row r="17" ht="26.85" customHeight="1" s="9">
+    <row r="17" s="9">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Collecting unemployment?</t>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="26.85" customHeight="1" s="9">
+    <row r="18" s="9">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Wins with numbers</t>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="9">
+    <row r="19" s="9">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Profile last updated</t>
@@ -1072,36 +1072,35 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="15" customHeight="1" s="9">
+    <row r="21" s="9">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>How to use this tab</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="9">
+    <row r="22" s="9">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>1. After Intake, click B2 and paste the answer block. Your answers fill B2 through B19.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="9">
+    <row r="23" s="9">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>2. To change one answer later, ask Claude to 'update my profile'. It tells you which cell to paste into.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="9">
+    <row r="24" s="9">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Yellow cells are yours to fill. Column C is a fictional example.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="9">
+    <row r="25" s="9">
       <c r="A25" s="16" t="n"/>
     </row>
   </sheetData>

--- a/sheet/fitfactoros-template.xlsx
+++ b/sheet/fitfactoros-template.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interviews" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profile" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interviews" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -20,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -93,8 +96,36 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -113,14 +144,29 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8DC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="6">
@@ -133,7 +179,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -186,6 +232,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -256,6 +313,80 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Jobs at each rung</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$27:$A$35</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$27:$B$35</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,6 +640,33 @@
 </comments>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -686,6 +844,449 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" style="9" min="1" max="1"/>
+    <col width="16" customWidth="1" style="9" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="3" max="3"/>
+    <col width="50" customWidth="1" style="9" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>FitFactorOS Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Updates on its own as you paste rows into the other tabs. Example rows are ignored. Nothing to type here except the yellow cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>This week (Sunday to Saturday)</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Week starts</t>
+        </is>
+      </c>
+      <c r="B5" s="23">
+        <f>TODAY()-WEEKDAY(TODAY())+1</f>
+        <v/>
+      </c>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Week ends</t>
+        </is>
+      </c>
+      <c r="B6" s="23">
+        <f>B5+6</f>
+        <v/>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Jobs screened this week</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$B$2:$B$1000,"&gt;="&amp;$B$5,Jobs!$B$2:$B$1000,"&lt;="&amp;$B$6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Every job you fit factor, including Passes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Activities this week that count for unemployment</t>
+        </is>
+      </c>
+      <c r="B8" s="25">
+        <f>COUNTIFS(Activity!$J$2:$J$1000,"Yes",Activity!$A$2:$A$1000,"&gt;="&amp;$B$5,Activity!$A$2:$A$1000,"&lt;="&amp;$B$6)</f>
+        <v/>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Rows on the Activity tab marked Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Your state's weekly minimum</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Type your state's number. Massachusetts asks for at least 3. Check your state's current rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>On track this week?</t>
+        </is>
+      </c>
+      <c r="B10" s="25">
+        <f>IF(B7+B8&gt;=B9,"On track","Need "&amp;(B9-B7-B8)&amp;" more")</f>
+        <v/>
+      </c>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Rough check: screened jobs plus activities. Your weekly log gives the exact count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Your search so far</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Jobs screened</t>
+        </is>
+      </c>
+      <c r="B13" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE")</f>
+        <v/>
+      </c>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="B14" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$M$2:$M$1000,"Pursue")</f>
+        <v/>
+      </c>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="B15" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$M$2:$M$1000,"Maybe")</f>
+        <v/>
+      </c>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$M$2:$M$1000,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Active leads</t>
+        </is>
+      </c>
+      <c r="B17" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$S$2:$S$1000,"Active")</f>
+        <v/>
+      </c>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Interviews logged</t>
+        </is>
+      </c>
+      <c r="B18" s="25">
+        <f>COUNTIFS(Interviews!$B$2:$B$1000,"&lt;&gt;",Interviews!$A$2:$A$1000,"&lt;&gt;*EXAMPLE")</f>
+        <v/>
+      </c>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Warm vs cold: your own results</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="B21" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$N$2:$N$1000,"Warm")</f>
+        <v/>
+      </c>
+      <c r="C21" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$N$2:$N$1000,"Cold")</f>
+        <v/>
+      </c>
+      <c r="D21" s="24" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Reached Applied or further</t>
+        </is>
+      </c>
+      <c r="B22" s="25">
+        <f>SUMPRODUCT(COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$N$2:$N$1000,"Warm",Jobs!$P$2:$P$1000,{"Applied","Heard back","Interviewing","Offer"}))</f>
+        <v/>
+      </c>
+      <c r="C22" s="25">
+        <f>SUMPRODUCT(COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$N$2:$N$1000,"Cold",Jobs!$P$2:$P$1000,{"Applied","Heard back","Interviewing","Offer"}))</f>
+        <v/>
+      </c>
+      <c r="D22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Reached Interviewing or further</t>
+        </is>
+      </c>
+      <c r="B23" s="25">
+        <f>SUMPRODUCT(COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$N$2:$N$1000,"Warm",Jobs!$P$2:$P$1000,{"Interviewing","Offer"}))</f>
+        <v/>
+      </c>
+      <c r="C23" s="25">
+        <f>SUMPRODUCT(COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$N$2:$N$1000,"Cold",Jobs!$P$2:$P$1000,{"Interviewing","Offer"}))</f>
+        <v/>
+      </c>
+      <c r="D23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Leads that became interviews</t>
+        </is>
+      </c>
+      <c r="B24" s="28">
+        <f>IFERROR(B23/B21,"—")</f>
+        <v/>
+      </c>
+      <c r="C24" s="28">
+        <f>IFERROR(C23/C21,"—")</f>
+        <v/>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Your numbers, not borrowed stats. Small counts swing a lot, so read this after 10+ leads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>The ladder: where your jobs are now</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Picked</t>
+        </is>
+      </c>
+      <c r="B27" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Picked")</f>
+        <v/>
+      </c>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Rungs only move for real steps. Warm paths often skip the middle rungs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Researched</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Researched")</f>
+        <v/>
+      </c>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Found the right person</t>
+        </is>
+      </c>
+      <c r="B29" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Found the right person")</f>
+        <v/>
+      </c>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Reached out to contact</t>
+        </is>
+      </c>
+      <c r="B30" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Reached out to contact")</f>
+        <v/>
+      </c>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Sent a researched note</t>
+        </is>
+      </c>
+      <c r="B31" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Sent a researched note")</f>
+        <v/>
+      </c>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="B32" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Applied")</f>
+        <v/>
+      </c>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Heard back</t>
+        </is>
+      </c>
+      <c r="B33" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Heard back")</f>
+        <v/>
+      </c>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Interviewing</t>
+        </is>
+      </c>
+      <c r="B34" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Interviewing")</f>
+        <v/>
+      </c>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="B35" s="25">
+        <f>COUNTIFS(Jobs!$A$2:$A$1000,"J-*",Jobs!$A$2:$A$1000,"&lt;&gt;*EXAMPLE",Jobs!$P$2:$P$1000,"Offer")</f>
+        <v/>
+      </c>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -1135,7 +1736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24362,7 +24963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34464,7 +35065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47577,7 +48178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/sheet/fitfactoros-template.xlsx
+++ b/sheet/fitfactoros-template.xlsx
@@ -179,7 +179,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -243,6 +243,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -317,7 +318,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="8" min="1" max="1"/>
@@ -1697,36 +1697,114 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Morning email sparks</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Quote; Music</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Morning email setup (optional)</t>
+        </is>
+      </c>
+    </row>
     <row r="21" s="9">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Sign (optional)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Capricorn</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Morning email setup (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="9">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Morning email ready by</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>7:00 am</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Morning email setup (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="9">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard link</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Morning email setup (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="9"/>
+    <row r="25" s="9"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>How to use this tab</t>
         </is>
       </c>
     </row>
-    <row r="22" s="9">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>1. After Intake, click B2 and paste the answer block. Your answers fill B2 through B19.</t>
         </is>
       </c>
     </row>
-    <row r="23" s="9">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>2. To change one answer later, ask Claude to 'update my profile'. It tells you which cell to paste into.</t>
         </is>
       </c>
     </row>
-    <row r="24" s="9">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>3. Optional: say 'set up my morning email' and paste its 4 answers into B20 through B23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>Yellow cells are yours to fill. Column C is a fictional example.</t>
         </is>
       </c>
-    </row>
-    <row r="25" s="9">
-      <c r="A25" s="16" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/sheet/fitfactoros-template.xlsx
+++ b/sheet/fitfactoros-template.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B10" s="25">
-        <f>IF(B7+B8&gt;=B9,"On track","Need "&amp;(B9-B7-B8)&amp;" more")</f>
+        <f>IF(B8&gt;=B9,"On track","Need "&amp;(B9-B8)&amp;" more")</f>
         <v/>
       </c>
       <c r="C10" s="24" t="n"/>

--- a/sheet/fitfactoros-template.xlsx
+++ b/sheet/fitfactoros-template.xlsx
@@ -970,7 +970,7 @@
       <c r="C10" s="24" t="n"/>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t>Rough check: screened jobs plus activities. Your weekly log gives the exact count.</t>
+          <t>Counts only Activity rows marked Yes. Screened jobs count once your weekly log adds them as Reviewed job posting rows.</t>
         </is>
       </c>
     </row>
